--- a/Excel Templates/column-ingestion-template-simple.xlsx
+++ b/Excel Templates/column-ingestion-template-simple.xlsx
@@ -460,8 +460,8 @@
     </comment>
     <comment ref="F1" authorId="0" shapeId="0">
       <text>
-        <t>Only if the column covers an area. A POINT here is rejected; use lat/lng.
-Format: POLYGON((lng lat, ...))</t>
+        <t>Only if the column covers an area (a POLYGON) or follows a measured traverse (a LINESTRING). A POINT here is rejected; use lat/lng.
+Format: POLYGON((lng lat, ...)) or LINESTRING(lng lat, ...)</t>
       </text>
     </comment>
     <comment ref="G1" authorId="0" shapeId="0">
@@ -518,8 +518,8 @@
     </comment>
     <comment ref="G1" authorId="0" shapeId="0">
       <text>
-        <t>Only if the column covers an area. A POINT here is rejected; use lat/lng.
-Format: POLYGON((lng lat, ...))</t>
+        <t>Only if the column covers an area (a POLYGON) or follows a measured traverse (a LINESTRING). A POINT here is rejected; use lat/lng.
+Format: POLYGON((lng lat, ...)) or LINESTRING(lng lat, ...)</t>
       </text>
     </comment>
     <comment ref="H1" authorId="0" shapeId="0">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Every column has lat + lng (or a POLYGON in geom; a POINT is rejected).</t>
+          <t>Every column has lat + lng, or a POLYGON or LINESTRING in geom (a POINT is rejected).</t>
         </is>
       </c>
     </row>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="G2" s="26" t="inlineStr">
         <is>
-          <t>Only if the column covers an area. A POINT here is rejected; use lat/lng.</t>
+          <t>Only if the column covers an area (a POLYGON) or follows a measured traverse (a LINESTRING). A POINT here is rejected; use lat/lng.</t>
         </is>
       </c>
       <c r="H2" s="26" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="G3" s="27" t="inlineStr">
         <is>
-          <t>POLYGON((lng lat, ...))</t>
+          <t>POLYGON((lng lat, ...)) or LINESTRING(lng lat, ...)</t>
         </is>
       </c>
       <c r="H3" s="27" t="inlineStr">

--- a/Excel Templates/column-ingestion-template-simple.xlsx
+++ b/Excel Templates/column-ingestion-template-simple.xlsx
@@ -558,55 +558,49 @@
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
+        <t>Formation or member name, as named in Macrostrat. Fill strat_name, unit_name, or both: each unit needs at least one. If unit_name is blank, this becomes the unit's name.
+Format: Text</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>A local name for the unit (e.g. "upper carbonate"). Fill unit_name, strat_name, or both: each unit needs at least one. If both are filled, this is the unit's name. Write "covered" for a covered interval, or "gap" at the base of missing rock.
+Format: Text</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
         <t>What the rock is: descriptive words, then the rock name. Write "covered" for a covered interval of unknown rock.
 Format: Text; several lithologies separated by ; (names at dev.macrostrat.org/lex/lithologies)
 See https://dev.macrostrat.org/lex/lithologies</t>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0">
-      <text>
-        <t>"y" if the unit is covered: present but not exposed. Its lithology is then your best inference (e.g. shale for a recessive interval).
-Format: y, or blank</t>
-      </text>
-    </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
-      <text>
-        <t>Formation or member name, as named in Macrostrat. Fill strat_name, unit_name, or both: each unit needs at least one. If unit_name is blank, this becomes the unit's name.
-Format: Text</t>
-      </text>
-    </comment>
     <comment ref="F1" authorId="0" shapeId="0">
-      <text>
-        <t>A local name for the unit (e.g. "upper carbonate"). Fill unit_name, strat_name, or both: each unit needs at least one. If both are filled, this is the unit's name. Write "covered" for a covered interval, or "gap" at the base of missing rock.
-Format: Text</t>
-      </text>
-    </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
       <text>
         <t>AGE AT THE BOTTOM of this unit, as a geologic time interval. Fill only at tie points (where you know the age); at least 2 per column. Ages in between are interpolated.
 Format: Macrostrat interval name (look it up at dev.macrostrat.org/lex/intervals)
 See https://dev.macrostrat.org/lex/intervals</t>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0">
+    <comment ref="G1" authorId="0" shapeId="0">
       <text>
         <t>WHERE IN THAT INTERVAL the bottom falls: 0 = start (oldest) of the interval, 0.5 = middle, 1 = end (youngest). A blank counts as 0, so give a best guess.
 Format: Number from 0 to 1</t>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0">
+    <comment ref="H1" authorId="0" shapeId="0">
       <text>
         <t>Why you chose each age tie point and proportion.
 Format: Text</t>
       </text>
     </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional: the facies_id of a facies on the facies tab. Wherever this unit leaves its own lithology or environment blank, it takes the facies'; its own cells always win.
+Format: A facies_id, e.g. F1</t>
+      </text>
+    </comment>
     <comment ref="J1" authorId="0" shapeId="0">
-      <text>
-        <t>Optional: the facies_id of a facies on the facies tab. The facies tab is not read on upload yet, so still fill lithology.
-Format: A facies_id, e.g. F1</t>
-      </text>
-    </comment>
-    <comment ref="K1" authorId="0" shapeId="0">
       <text>
         <t>Generalizations, gaps, anything a reader should know.
 Format: Text</t>
@@ -636,55 +630,49 @@
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
       <text>
+        <t>Formation or member name, as named in Macrostrat. Fill strat_name, unit_name, or both: each unit needs at least one. If unit_name is blank, this becomes the unit's name.
+Format: Text</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>A local name for the unit (e.g. "upper carbonate"). Fill unit_name, strat_name, or both: each unit needs at least one. If both are filled, this is the unit's name. Write "covered" for a covered interval, or "gap" at the base of missing rock.
+Format: Text</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
         <t>What the rock is: descriptive words, then the rock name. Write "covered" for a covered interval of unknown rock.
 Format: Text; several lithologies separated by ; (names at dev.macrostrat.org/lex/lithologies)
 See https://dev.macrostrat.org/lex/lithologies</t>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
-      <text>
-        <t>"y" if the unit is covered: present but not exposed. Its lithology is then your best inference (e.g. shale for a recessive interval).
-Format: y, or blank</t>
-      </text>
-    </comment>
-    <comment ref="F1" authorId="0" shapeId="0">
-      <text>
-        <t>Formation or member name, as named in Macrostrat. Fill strat_name, unit_name, or both: each unit needs at least one. If unit_name is blank, this becomes the unit's name.
-Format: Text</t>
-      </text>
-    </comment>
     <comment ref="G1" authorId="0" shapeId="0">
-      <text>
-        <t>A local name for the unit (e.g. "upper carbonate"). Fill unit_name, strat_name, or both: each unit needs at least one. If both are filled, this is the unit's name. Write "covered" for a covered interval, or "gap" at the base of missing rock.
-Format: Text</t>
-      </text>
-    </comment>
-    <comment ref="H1" authorId="0" shapeId="0">
       <text>
         <t>AGE AT THE BOTTOM of this unit, as a geologic time interval. Fill only at tie points (where you know the age); at least 2 per column. Ages in between are interpolated.
 Format: Macrostrat interval name (look it up at dev.macrostrat.org/lex/intervals)
 See https://dev.macrostrat.org/lex/intervals</t>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0">
+    <comment ref="H1" authorId="0" shapeId="0">
       <text>
         <t>WHERE IN THAT INTERVAL the bottom falls: 0 = start (oldest) of the interval, 0.5 = middle, 1 = end (youngest). A blank counts as 0, so give a best guess.
 Format: Number from 0 to 1</t>
       </text>
     </comment>
-    <comment ref="J1" authorId="0" shapeId="0">
+    <comment ref="I1" authorId="0" shapeId="0">
       <text>
         <t>Why you chose each age tie point and proportion.
 Format: Text</t>
       </text>
     </comment>
+    <comment ref="J1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional: the facies_id of a facies on the facies tab. Wherever this unit leaves its own lithology or environment blank, it takes the facies'; its own cells always win.
+Format: A facies_id, e.g. F1</t>
+      </text>
+    </comment>
     <comment ref="K1" authorId="0" shapeId="0">
-      <text>
-        <t>Optional: the facies_id of a facies on the facies tab. The facies tab is not read on upload yet, so still fill lithology.
-Format: A facies_id, e.g. F1</t>
-      </text>
-    </comment>
-    <comment ref="L1" authorId="0" shapeId="0">
       <text>
         <t>Generalizations, gaps, anything a reader should know.
 Format: Text</t>
@@ -716,7 +704,7 @@
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
         <t>Depositional environment(s) of the facies.
-Format: Text; several separated by ; (names at dev.macrostrat.org/lex/environments)
+Format: Text; several separated by ; or , (names at dev.macrostrat.org/lex/environments)
 See https://dev.macrostrat.org/lex/environments</t>
       </text>
     </comment>
@@ -752,7 +740,7 @@
     <comment ref="D1" authorId="0" shapeId="0">
       <text>
         <t>Depositional environment(s) of the facies.
-Format: Text; several separated by ; (names at dev.macrostrat.org/lex/environments)
+Format: Text; several separated by ; or , (names at dev.macrostrat.org/lex/environments)
 See https://dev.macrostrat.org/lex/environments</t>
       </text>
     </comment>
@@ -1545,7 +1533,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Lithology is on every unit (the facies tab is NOT read by the ingester yet).</t>
+          <t>Every unit has a lithology, of its own or from its facies.</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1545,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Covered intervals are units named covered (or covered = y), and missing rock is a row named gap.</t>
+          <t>Covered intervals are units named covered, and missing rock is a row named gap.</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1658,7 @@
     <row r="54" ht="32" customHeight="1">
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Covered intervals: add a unit named covered (as its unit_name or lithology), or set covered = y on a unit and give your best inference of its lithology.</t>
+          <t>Covered intervals: add a unit named covered (as its unit_name or lithology).</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1672,7 @@
     <row r="56" ht="32" customHeight="1">
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Extra tabs (this one, the example tabs, facies and images) are ignored on upload.</t>
+          <t>Extra tabs (this one, the example tabs and images) are ignored on upload.</t>
         </is>
       </c>
     </row>
@@ -2785,20 +2773,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="36" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="40" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2812,56 +2799,51 @@
           <t>position</t>
         </is>
       </c>
-      <c r="C1" s="21" t="inlineStr">
+      <c r="C1" s="30" t="inlineStr">
+        <is>
+          <t>strat_name</t>
+        </is>
+      </c>
+      <c r="D1" s="30" t="inlineStr">
+        <is>
+          <t>unit_name</t>
+        </is>
+      </c>
+      <c r="E1" s="21" t="inlineStr">
         <is>
           <t>lithology</t>
         </is>
       </c>
-      <c r="D1" s="23" t="inlineStr">
-        <is>
-          <t>covered</t>
-        </is>
-      </c>
-      <c r="E1" s="30" t="inlineStr">
-        <is>
-          <t>strat_name</t>
-        </is>
-      </c>
-      <c r="F1" s="30" t="inlineStr">
-        <is>
-          <t>unit_name</t>
+      <c r="F1" s="31" t="inlineStr">
+        <is>
+          <t>b_int</t>
         </is>
       </c>
       <c r="G1" s="31" t="inlineStr">
         <is>
-          <t>b_int</t>
-        </is>
-      </c>
-      <c r="H1" s="31" t="inlineStr">
-        <is>
           <t>b_prop</t>
         </is>
       </c>
-      <c r="I1" s="22" t="inlineStr">
+      <c r="H1" s="22" t="inlineStr">
         <is>
           <t>age_model_notes</t>
         </is>
       </c>
-      <c r="J1" s="23" t="inlineStr">
+      <c r="I1" s="23" t="inlineStr">
         <is>
           <t>facies</t>
         </is>
       </c>
-      <c r="K1" s="22" t="inlineStr">
+      <c r="J1" s="22" t="inlineStr">
         <is>
           <t>comments</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E2:F2000">
+  <conditionalFormatting sqref="C2:D2000">
     <cfRule type="expression" priority="1" dxfId="1">
-      <formula>AND($A2&lt;&gt;"",$E2="",$F2="")</formula>
+      <formula>AND($A2&lt;&gt;"",$C2="",$D2="")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
@@ -2871,7 +2853,7 @@
     <dataValidation sqref="B2:B2000" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" prompt="Base of the unit, metres above column base" type="decimal" errorStyle="stop" operator="greaterThan">
       <formula1>-100000</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H2000" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" prompt="0 = oldest end, 1 = youngest end" type="decimal" errorStyle="stop" operator="between">
+    <dataValidation sqref="G2:G2000" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" prompt="0 = oldest end, 1 = youngest end" type="decimal" errorStyle="stop" operator="between">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
@@ -2888,21 +2870,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="36" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="40" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="40" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2917,47 +2898,42 @@
           <t>position</t>
         </is>
       </c>
-      <c r="D1" s="21" t="inlineStr">
+      <c r="D1" s="30" t="inlineStr">
+        <is>
+          <t>strat_name</t>
+        </is>
+      </c>
+      <c r="E1" s="30" t="inlineStr">
+        <is>
+          <t>unit_name</t>
+        </is>
+      </c>
+      <c r="F1" s="21" t="inlineStr">
         <is>
           <t>lithology</t>
         </is>
       </c>
-      <c r="E1" s="23" t="inlineStr">
-        <is>
-          <t>covered</t>
-        </is>
-      </c>
-      <c r="F1" s="30" t="inlineStr">
-        <is>
-          <t>strat_name</t>
-        </is>
-      </c>
-      <c r="G1" s="30" t="inlineStr">
-        <is>
-          <t>unit_name</t>
+      <c r="G1" s="31" t="inlineStr">
+        <is>
+          <t>b_int</t>
         </is>
       </c>
       <c r="H1" s="31" t="inlineStr">
         <is>
-          <t>b_int</t>
-        </is>
-      </c>
-      <c r="I1" s="31" t="inlineStr">
-        <is>
           <t>b_prop</t>
         </is>
       </c>
-      <c r="J1" s="22" t="inlineStr">
+      <c r="I1" s="22" t="inlineStr">
         <is>
           <t>age_model_notes</t>
         </is>
       </c>
-      <c r="K1" s="23" t="inlineStr">
+      <c r="J1" s="23" t="inlineStr">
         <is>
           <t>facies</t>
         </is>
       </c>
-      <c r="L1" s="22" t="inlineStr">
+      <c r="K1" s="22" t="inlineStr">
         <is>
           <t>comments</t>
         </is>
@@ -2981,45 +2957,40 @@
       </c>
       <c r="D2" s="26" t="inlineStr">
         <is>
+          <t>Formation or member name, as named in Macrostrat. Fill strat_name, unit_name, or both: each unit needs at least one. If unit_name is blank, this becomes the unit's name.</t>
+        </is>
+      </c>
+      <c r="E2" s="26" t="inlineStr">
+        <is>
+          <t>A local name for the unit (e.g. "upper carbonate"). Fill unit_name, strat_name, or both: each unit needs at least one. If both are filled, this is the unit's name. Write "covered" for a covered interval, or "gap" at the base of missing rock.</t>
+        </is>
+      </c>
+      <c r="F2" s="26" t="inlineStr">
+        <is>
           <t>What the rock is: descriptive words, then the rock name. Write "covered" for a covered interval of unknown rock.</t>
         </is>
       </c>
-      <c r="E2" s="26" t="inlineStr">
-        <is>
-          <t>"y" if the unit is covered: present but not exposed. Its lithology is then your best inference (e.g. shale for a recessive interval).</t>
-        </is>
-      </c>
-      <c r="F2" s="26" t="inlineStr">
-        <is>
-          <t>Formation or member name, as named in Macrostrat. Fill strat_name, unit_name, or both: each unit needs at least one. If unit_name is blank, this becomes the unit's name.</t>
-        </is>
-      </c>
       <c r="G2" s="26" t="inlineStr">
         <is>
-          <t>A local name for the unit (e.g. "upper carbonate"). Fill unit_name, strat_name, or both: each unit needs at least one. If both are filled, this is the unit's name. Write "covered" for a covered interval, or "gap" at the base of missing rock.</t>
+          <t>AGE AT THE BOTTOM of this unit, as a geologic time interval. Fill only at tie points (where you know the age); at least 2 per column. Ages in between are interpolated.</t>
         </is>
       </c>
       <c r="H2" s="26" t="inlineStr">
         <is>
-          <t>AGE AT THE BOTTOM of this unit, as a geologic time interval. Fill only at tie points (where you know the age); at least 2 per column. Ages in between are interpolated.</t>
+          <t>WHERE IN THAT INTERVAL the bottom falls: 0 = start (oldest) of the interval, 0.5 = middle, 1 = end (youngest). A blank counts as 0, so give a best guess.</t>
         </is>
       </c>
       <c r="I2" s="26" t="inlineStr">
         <is>
-          <t>WHERE IN THAT INTERVAL the bottom falls: 0 = start (oldest) of the interval, 0.5 = middle, 1 = end (youngest). A blank counts as 0, so give a best guess.</t>
+          <t>Why you chose each age tie point and proportion.</t>
         </is>
       </c>
       <c r="J2" s="26" t="inlineStr">
         <is>
-          <t>Why you chose each age tie point and proportion.</t>
+          <t>Optional: the facies_id of a facies on the facies tab. Wherever this unit leaves its own lithology or environment blank, it takes the facies'; its own cells always win.</t>
         </is>
       </c>
       <c r="K2" s="26" t="inlineStr">
-        <is>
-          <t>Optional: the facies_id of a facies on the facies tab. The facies tab is not read on upload yet, so still fill lithology.</t>
-        </is>
-      </c>
-      <c r="L2" s="26" t="inlineStr">
         <is>
           <t>Generalizations, gaps, anything a reader should know.</t>
         </is>
@@ -3041,47 +3012,42 @@
           <t>Number (metres)</t>
         </is>
       </c>
-      <c r="D3" s="32" t="inlineStr">
+      <c r="D3" s="27" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E3" s="27" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F3" s="32" t="inlineStr">
         <is>
           <t>Text; several lithologies separated by ; (names at dev.macrostrat.org/lex/lithologies)</t>
         </is>
       </c>
-      <c r="E3" s="27" t="inlineStr">
-        <is>
-          <t>y, or blank</t>
-        </is>
-      </c>
-      <c r="F3" s="27" t="inlineStr">
+      <c r="G3" s="32" t="inlineStr">
+        <is>
+          <t>Macrostrat interval name (look it up at dev.macrostrat.org/lex/intervals)</t>
+        </is>
+      </c>
+      <c r="H3" s="27" t="inlineStr">
+        <is>
+          <t>Number from 0 to 1</t>
+        </is>
+      </c>
+      <c r="I3" s="27" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="G3" s="27" t="inlineStr">
-        <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="H3" s="32" t="inlineStr">
-        <is>
-          <t>Macrostrat interval name (look it up at dev.macrostrat.org/lex/intervals)</t>
-        </is>
-      </c>
-      <c r="I3" s="27" t="inlineStr">
-        <is>
-          <t>Number from 0 to 1</t>
-        </is>
-      </c>
       <c r="J3" s="27" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>A facies_id, e.g. F1</t>
         </is>
       </c>
       <c r="K3" s="27" t="inlineStr">
-        <is>
-          <t>A facies_id, e.g. F1</t>
-        </is>
-      </c>
-      <c r="L3" s="27" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
@@ -3108,8 +3074,7 @@
       <c r="H4" s="29" t="n"/>
       <c r="I4" s="29" t="n"/>
       <c r="J4" s="29" t="n"/>
-      <c r="K4" s="29" t="n"/>
-      <c r="L4" s="17" t="inlineStr">
+      <c r="K4" s="17" t="inlineStr">
         <is>
           <t>Empty closing row: the top of the measured section.</t>
         </is>
@@ -3131,21 +3096,20 @@
       </c>
       <c r="D5" s="29" t="inlineStr">
         <is>
-          <t>cross-stratified sandstone</t>
+          <t>Wood Canyon Formation</t>
         </is>
       </c>
       <c r="E5" s="29" t="n"/>
       <c r="F5" s="29" t="inlineStr">
         <is>
-          <t>Wood Canyon Formation</t>
+          <t>cross-stratified sandstone</t>
         </is>
       </c>
       <c r="G5" s="29" t="n"/>
       <c r="H5" s="29" t="n"/>
       <c r="I5" s="29" t="n"/>
       <c r="J5" s="29" t="n"/>
-      <c r="K5" s="29" t="n"/>
-      <c r="L5" s="17" t="inlineStr">
+      <c r="K5" s="17" t="inlineStr">
         <is>
           <t>Runs up to the closing row (7.54 m).</t>
         </is>
@@ -3167,13 +3131,13 @@
       </c>
       <c r="D6" s="29" t="inlineStr">
         <is>
-          <t>pebble, cobble conglomerate</t>
+          <t>Wood Canyon Formation</t>
         </is>
       </c>
       <c r="E6" s="29" t="n"/>
       <c r="F6" s="29" t="inlineStr">
         <is>
-          <t>Wood Canyon Formation</t>
+          <t>pebble, cobble conglomerate</t>
         </is>
       </c>
       <c r="G6" s="29" t="n"/>
@@ -3181,7 +3145,6 @@
       <c r="I6" s="29" t="n"/>
       <c r="J6" s="29" t="n"/>
       <c r="K6" s="29" t="n"/>
-      <c r="L6" s="29" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="28" t="inlineStr">
@@ -3197,23 +3160,22 @@
       <c r="C7" s="29" t="n">
         <v>4.93</v>
       </c>
-      <c r="D7" s="29" t="n"/>
-      <c r="E7" s="29" t="n"/>
-      <c r="F7" s="29" t="inlineStr">
+      <c r="D7" s="29" t="inlineStr">
         <is>
           <t>Wood Canyon Formation</t>
         </is>
       </c>
-      <c r="G7" s="29" t="inlineStr">
+      <c r="E7" s="29" t="inlineStr">
         <is>
           <t>covered</t>
         </is>
       </c>
+      <c r="F7" s="29" t="n"/>
+      <c r="G7" s="29" t="n"/>
       <c r="H7" s="29" t="n"/>
       <c r="I7" s="29" t="n"/>
       <c r="J7" s="29" t="n"/>
-      <c r="K7" s="29" t="n"/>
-      <c r="L7" s="29" t="inlineStr">
+      <c r="K7" s="29" t="inlineStr">
         <is>
           <t>Covered interval.</t>
         </is>
@@ -3235,31 +3197,30 @@
       </c>
       <c r="D8" s="29" t="inlineStr">
         <is>
-          <t>pebble, cobble conglomerate</t>
+          <t>Wood Canyon Formation</t>
         </is>
       </c>
       <c r="E8" s="29" t="n"/>
       <c r="F8" s="29" t="inlineStr">
         <is>
-          <t>Wood Canyon Formation</t>
-        </is>
-      </c>
-      <c r="G8" s="29" t="n"/>
-      <c r="H8" s="29" t="inlineStr">
+          <t>pebble, cobble conglomerate</t>
+        </is>
+      </c>
+      <c r="G8" s="29" t="inlineStr">
         <is>
           <t>Terreneuvian</t>
         </is>
       </c>
-      <c r="I8" s="29" t="n">
+      <c r="H8" s="29" t="n">
         <v>0.75</v>
       </c>
-      <c r="J8" s="17" t="inlineStr">
+      <c r="I8" s="17" t="inlineStr">
         <is>
           <t>Placeholder age: base and datum tied within the Terreneuvian; proportions are best guesses.</t>
         </is>
       </c>
-      <c r="K8" s="29" t="n"/>
-      <c r="L8" s="17" t="inlineStr">
+      <c r="J8" s="29" t="n"/>
+      <c r="K8" s="17" t="inlineStr">
         <is>
           <t>Datum bed: age tie point, same b_int/b_prop in every column.</t>
         </is>
@@ -3281,31 +3242,30 @@
       </c>
       <c r="D9" s="29" t="inlineStr">
         <is>
-          <t>cross-stratified sandstone</t>
+          <t>Wood Canyon Formation</t>
         </is>
       </c>
       <c r="E9" s="29" t="n"/>
       <c r="F9" s="29" t="inlineStr">
         <is>
-          <t>Wood Canyon Formation</t>
-        </is>
-      </c>
-      <c r="G9" s="29" t="n"/>
-      <c r="H9" s="29" t="inlineStr">
+          <t>cross-stratified sandstone</t>
+        </is>
+      </c>
+      <c r="G9" s="29" t="inlineStr">
         <is>
           <t>Terreneuvian</t>
         </is>
       </c>
-      <c r="I9" s="29" t="n">
+      <c r="H9" s="29" t="n">
         <v>0.5</v>
       </c>
-      <c r="J9" s="17" t="inlineStr">
+      <c r="I9" s="17" t="inlineStr">
         <is>
           <t>Placeholder age: base and datum tied within the Terreneuvian; proportions are best guesses.</t>
         </is>
       </c>
-      <c r="K9" s="29" t="n"/>
-      <c r="L9" s="17" t="inlineStr">
+      <c r="J9" s="29" t="n"/>
+      <c r="K9" s="17" t="inlineStr">
         <is>
           <t>Base of column (position = 0): age tie point.</t>
         </is>
@@ -3320,8 +3280,8 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -3457,7 +3417,7 @@
       </c>
       <c r="D3" s="32" t="inlineStr">
         <is>
-          <t>Text; several separated by ; (names at dev.macrostrat.org/lex/environments)</t>
+          <t>Text; several separated by ; or , (names at dev.macrostrat.org/lex/environments)</t>
         </is>
       </c>
       <c r="E3" s="27" t="inlineStr">
